--- a/reference/H743飞控/BOM_Drone_FC_v1.2_h743fc_mainboard_v1.2_2024-11-25.xlsx
+++ b/reference/H743飞控/BOM_Drone_FC_v1.2_h743fc_mainboard_v1.2_2024-11-25.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD615B21-157C-4E32-8CCA-8F3B5E540394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60634718-F22F-419A-9F2E-0DAE01D2CFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Drone_FC_v1.2_h743fc_mainbo" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="223">
   <si>
     <t>No.</t>
   </si>
@@ -731,6 +731,10 @@
   </si>
   <si>
     <t>0603 LED-RED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R0603</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1116,17 +1120,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="71.5" customWidth="1"/>
-    <col min="4" max="4" width="49.625" customWidth="1"/>
+    <col min="3" max="3" width="71.453125" customWidth="1"/>
+    <col min="4" max="4" width="49.6328125" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="27.75" customWidth="1"/>
-    <col min="7" max="7" width="30.75" customWidth="1"/>
+    <col min="6" max="6" width="27.7265625" customWidth="1"/>
+    <col min="7" max="7" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1149,7 +1153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1172,7 +1176,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1195,7 +1199,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1218,7 +1222,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1241,7 +1245,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1264,7 +1268,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1287,7 +1291,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1310,7 +1314,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1333,7 +1337,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1356,7 +1360,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1379,7 +1383,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1402,7 +1406,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>140</v>
       </c>
@@ -1425,7 +1429,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1448,7 +1452,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1494,7 +1498,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -1517,7 +1521,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -1540,7 +1544,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -1563,7 +1567,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -1586,7 +1590,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -1609,7 +1613,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -1632,7 +1636,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -1655,7 +1659,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>73</v>
       </c>
@@ -1678,7 +1682,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -1701,7 +1705,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -1724,7 +1728,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -1747,7 +1751,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>85</v>
       </c>
@@ -1770,7 +1774,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>88</v>
       </c>
@@ -1781,7 +1785,7 @@
         <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>222</v>
       </c>
       <c r="E29" t="s">
         <v>90</v>
@@ -1793,7 +1797,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -1816,7 +1820,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>95</v>
       </c>
@@ -1839,7 +1843,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>98</v>
       </c>
@@ -1862,7 +1866,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -1885,7 +1889,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>106</v>
       </c>
@@ -1908,7 +1912,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>110</v>
       </c>
@@ -1931,7 +1935,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>114</v>
       </c>
@@ -1954,7 +1958,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -1977,7 +1981,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2000,7 +2004,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>125</v>
       </c>
@@ -2023,7 +2027,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>128</v>
       </c>
@@ -2046,7 +2050,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -2069,7 +2073,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>136</v>
       </c>
@@ -2092,7 +2096,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -2115,7 +2119,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>148</v>
       </c>
@@ -2138,7 +2142,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -2161,7 +2165,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>156</v>
       </c>
@@ -2184,7 +2188,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>159</v>
       </c>
@@ -2207,7 +2211,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>163</v>
       </c>
@@ -2230,7 +2234,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>168</v>
       </c>
@@ -2253,7 +2257,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>13</v>
       </c>
